--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46407A75-D542-4330-8DF9-ADAE9BB06593}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F81CBDF4-4294-423B-AF99-8542213B36DA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{603A7FC1-D077-430C-9EF9-8A3DB62CFFDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDFC3167-FB92-4D48-84AB-8177EE2DB328}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC705523-D98E-4414-BFCB-75ED916E6E91}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EE8A916-E861-4340-9BDE-B5E6C9E15626}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F81CBDF4-4294-423B-AF99-8542213B36DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16D5A710-B872-4442-928B-967938416068}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDFC3167-FB92-4D48-84AB-8177EE2DB328}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D67EC21-912B-40ED-A00E-10C8CD26CAAB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EE8A916-E861-4340-9BDE-B5E6C9E15626}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2CEB240-DFEB-4659-B528-0388E8A7E926}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16D5A710-B872-4442-928B-967938416068}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0793640-A39B-4166-8A0B-6CAEB37003D4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D67EC21-912B-40ED-A00E-10C8CD26CAAB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEF3C438-A102-4180-BB60-CC117213C5E3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2CEB240-DFEB-4659-B528-0388E8A7E926}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E73D3F5F-2AE4-48ED-BE78-0622DB18B661}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0793640-A39B-4166-8A0B-6CAEB37003D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50CD8C8D-D882-4138-86E8-581DD91D91F1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEF3C438-A102-4180-BB60-CC117213C5E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE63592E-0F86-4BCF-BCC4-5F62B22BB5A5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E73D3F5F-2AE4-48ED-BE78-0622DB18B661}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91E64EBE-C792-446C-94F3-4C6919853F9F}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50CD8C8D-D882-4138-86E8-581DD91D91F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7B09AB0-E445-4309-9722-E6C9CE3E6416}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE63592E-0F86-4BCF-BCC4-5F62B22BB5A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D8F55A8-BF24-4CE2-9756-3EAC2BBF7C5C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91E64EBE-C792-446C-94F3-4C6919853F9F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C3B66B9-82C6-4769-BC7E-9A1132947E3C}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4880,22 +4880,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0793640-A39B-4166-8A0B-6CAEB37003D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7ECECDC0-9759-4797-9D90-C27193E6DA95}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEF3C438-A102-4180-BB60-CC117213C5E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED0F05C9-8AB8-4921-8808-6A0212F2F4FB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E73D3F5F-2AE4-48ED-BE78-0622DB18B661}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57F80D6A-36AD-4A9C-BB10-B38F1E7F0C2F}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4880,22 +4880,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7B09AB0-E445-4309-9722-E6C9CE3E6416}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29A05BAF-6167-4DD3-AF8E-B7D170E82774}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D8F55A8-BF24-4CE2-9756-3EAC2BBF7C5C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32BD7469-6CC0-4D2F-9424-FEE09286EDF1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C3B66B9-82C6-4769-BC7E-9A1132947E3C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A1BFCC9-7BBF-482F-BF06-BC7D82C9AB42}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29A05BAF-6167-4DD3-AF8E-B7D170E82774}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F045283-2BA7-49FB-A19E-D9C0AC4385B9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32BD7469-6CC0-4D2F-9424-FEE09286EDF1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51EF4AF1-3411-48FA-AF23-5DBE79E4C569}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A1BFCC9-7BBF-482F-BF06-BC7D82C9AB42}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F15584F8-AC0A-45DD-8AFE-B1DF43A23D8E}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F045283-2BA7-49FB-A19E-D9C0AC4385B9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F31FE7FA-9164-41FE-95AF-0878097A6278}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51EF4AF1-3411-48FA-AF23-5DBE79E4C569}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A552517-C885-47C8-982C-A14A3F7CA8F0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F15584F8-AC0A-45DD-8AFE-B1DF43A23D8E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{313E9548-6D6F-4DE4-825C-B4AB26B72E11}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F31FE7FA-9164-41FE-95AF-0878097A6278}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8804A033-9337-43CD-A8BE-21B7066AC52E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A552517-C885-47C8-982C-A14A3F7CA8F0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E984D2F2-9E03-46BF-8134-91F24A422CCE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{313E9548-6D6F-4DE4-825C-B4AB26B72E11}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6257A6A6-24DE-4D9F-9F5F-B72BF9CEDBF2}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8804A033-9337-43CD-A8BE-21B7066AC52E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97243C09-8B6B-49FE-B8A0-68756D12201A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E984D2F2-9E03-46BF-8134-91F24A422CCE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57F64048-CF9A-42DA-A10E-C0BF1963CACB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6257A6A6-24DE-4D9F-9F5F-B72BF9CEDBF2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F77D562-E85C-42CB-9C2B-DCDBCE2C2F5B}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97243C09-8B6B-49FE-B8A0-68756D12201A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{570CC9FF-DB74-4996-B319-0101B9F8ADC4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57F64048-CF9A-42DA-A10E-C0BF1963CACB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3E3AE5-CB2F-4452-A8DC-BAE5CBA08D50}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F77D562-E85C-42CB-9C2B-DCDBCE2C2F5B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7F59CED-E58C-44E8-986E-26A4CB6569CE}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{570CC9FF-DB74-4996-B319-0101B9F8ADC4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23DA0759-C879-4FF7-AD9A-CF2E1EE8536D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3E3AE5-CB2F-4452-A8DC-BAE5CBA08D50}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A5B07E8-B19F-4977-8377-928B4B7F4C86}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7F59CED-E58C-44E8-986E-26A4CB6569CE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9693E392-1E3A-4D83-8197-E6BBB16B1EB3}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23DA0759-C879-4FF7-AD9A-CF2E1EE8536D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D7D3995-2DF6-4010-83D1-7FB1434078CC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A5B07E8-B19F-4977-8377-928B4B7F4C86}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A4A626A-BD2A-4BEF-9447-31484C0F6C9E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9693E392-1E3A-4D83-8197-E6BBB16B1EB3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9994EBD3-C4E3-4FA0-A725-5FB509A65EFD}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D7D3995-2DF6-4010-83D1-7FB1434078CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0784397-976E-41A5-AAD2-0022898AE722}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A4A626A-BD2A-4BEF-9447-31484C0F6C9E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18929AB6-F09E-4354-AC15-7239BAF54F1F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9994EBD3-C4E3-4FA0-A725-5FB509A65EFD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8457B138-DE44-4F85-B8DC-A78C989709E3}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0784397-976E-41A5-AAD2-0022898AE722}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15270483-9D92-4894-8007-43116F5C51AC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18929AB6-F09E-4354-AC15-7239BAF54F1F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5B6CFFB-BBC1-43C9-BD18-E374BA453CAD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8457B138-DE44-4F85-B8DC-A78C989709E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{481ED96B-79DD-4DEB-8CA5-C98BD03636F2}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15270483-9D92-4894-8007-43116F5C51AC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3526A4D-0E3F-4B40-8572-1C0146181038}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5B6CFFB-BBC1-43C9-BD18-E374BA453CAD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BC0BE2E-5CB7-429D-8CD6-C92F608E8048}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{481ED96B-79DD-4DEB-8CA5-C98BD03636F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9811E486-9140-426E-B231-D87485D0C8B5}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3526A4D-0E3F-4B40-8572-1C0146181038}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6335FADB-9B61-498C-A822-03174AB42733}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BC0BE2E-5CB7-429D-8CD6-C92F608E8048}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE6F076A-63E2-4B6F-8A16-A9EF509459FB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9811E486-9140-426E-B231-D87485D0C8B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9960641C-F63E-4F70-9132-0413F1EF4DA3}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6335FADB-9B61-498C-A822-03174AB42733}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A0AB3E5-2336-4EA0-AC72-00AA35BAE61A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE6F076A-63E2-4B6F-8A16-A9EF509459FB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD5984BF-BB33-4E35-BCD7-74C574D259E8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9960641C-F63E-4F70-9132-0413F1EF4DA3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A714EFE8-4D6B-4E0D-9EA1-FF221E6D9E63}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A0AB3E5-2336-4EA0-AC72-00AA35BAE61A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AD142D5-EF2F-4898-81D9-F3E3656064E6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD5984BF-BB33-4E35-BCD7-74C574D259E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DDC06F7-44E0-4786-ADE3-B2B3205358FF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A714EFE8-4D6B-4E0D-9EA1-FF221E6D9E63}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADFE4A3D-A0CC-40E1-B9C3-F2AFDADDFD8E}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AD142D5-EF2F-4898-81D9-F3E3656064E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80EB41E4-F083-4A82-A6AA-CE61110DC5C6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DDC06F7-44E0-4786-ADE3-B2B3205358FF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B2C9E72-215C-4221-B481-1C0B1DC58BB3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADFE4A3D-A0CC-40E1-B9C3-F2AFDADDFD8E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A8746F0-9C93-4A6A-BD32-EC3D5CCE9030}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80EB41E4-F083-4A82-A6AA-CE61110DC5C6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6FA5E7E-47FE-4BC2-8645-FEB073977DB4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B2C9E72-215C-4221-B481-1C0B1DC58BB3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D35BF52-AEB4-40A4-A0E4-45733FEBD401}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A8746F0-9C93-4A6A-BD32-EC3D5CCE9030}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34B19C56-6E16-43C8-A21B-52724FFB27D2}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6FA5E7E-47FE-4BC2-8645-FEB073977DB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D9B0D12-6916-4F24-8B2E-9C6858F5B445}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D35BF52-AEB4-40A4-A0E4-45733FEBD401}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6905B98-6918-4121-88A9-9AE0B53699B2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34B19C56-6E16-43C8-A21B-52724FFB27D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3726B924-D8E6-4FB3-9DA9-A5F630E0D5FA}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D9B0D12-6916-4F24-8B2E-9C6858F5B445}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{590C07D0-B228-45F8-9ECA-14664537920B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6905B98-6918-4121-88A9-9AE0B53699B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3BCDD84-04C0-4941-88D8-2060ADEE45B9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3726B924-D8E6-4FB3-9DA9-A5F630E0D5FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92126664-45F8-4888-9040-1429A07F355D}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{590C07D0-B228-45F8-9ECA-14664537920B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82CEA76A-C583-46D7-9960-ACDFF015C5AA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3BCDD84-04C0-4941-88D8-2060ADEE45B9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58A898AA-1722-4EBF-86DB-DCCAD8FE53CD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92126664-45F8-4888-9040-1429A07F355D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1429EAAB-6EAE-49BF-BE72-5EE3840FAC89}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82CEA76A-C583-46D7-9960-ACDFF015C5AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F07A3D85-EA19-4942-9D22-3E1C15ED1375}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58A898AA-1722-4EBF-86DB-DCCAD8FE53CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81F808C4-6715-484C-A2EE-3F7EE845E99A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1429EAAB-6EAE-49BF-BE72-5EE3840FAC89}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48580E6A-1616-4936-86A0-449E31A0FBA5}"/>
 </file>